--- a/exports/ETERNAL_full_report.xlsx
+++ b/exports/ETERNAL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q69"/>
+  <dimension ref="A1:U69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>5.63</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44580.55208333334</v>
+        <v>44581.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>129.45</v>
+        <v>126.15</v>
       </c>
       <c r="I2" t="n">
         <v>129.2752553031708</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K2" t="n">
-        <v>-0.77</v>
+        <v>-3.3</v>
       </c>
       <c r="L2" t="n">
-        <v>1.65</v>
+        <v>3.33</v>
       </c>
       <c r="M2" t="n">
-        <v>0.9399999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="N2" t="n">
-        <v>2.63</v>
+        <v>2.74</v>
       </c>
       <c r="O2" t="n">
         <v>0.73</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>6.53</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44650.38541666666</v>
+        <v>44650.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>81.40000000000001</v>
+        <v>86</v>
       </c>
       <c r="I3" t="n">
         <v>82.48640466883312</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>69</v>
+        <v>69.16666666666667</v>
       </c>
       <c r="K3" t="n">
-        <v>35.47</v>
+        <v>31.83</v>
       </c>
       <c r="L3" t="n">
         <v>3.61</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>10.52</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44676.55208333334</v>
+        <v>44677.38541666666</v>
       </c>
       <c r="H4" t="n">
-        <v>79</v>
+        <v>78.8</v>
       </c>
       <c r="I4" t="n">
         <v>78.88656531623295</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>26</v>
+        <v>26.83333333333333</v>
       </c>
       <c r="K4" t="n">
-        <v>-8.140000000000001</v>
+        <v>-8.369999999999999</v>
       </c>
       <c r="L4" t="n">
         <v>8.6</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>8.039999999999999</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44704.55208333334</v>
+        <v>44705.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>56.75</v>
+        <v>63.95</v>
       </c>
       <c r="I5" t="n">
         <v>60.6427699639716</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K5" t="n">
-        <v>27.98</v>
+        <v>18.85</v>
       </c>
       <c r="L5" t="n">
         <v>2.28</v>
@@ -726,7 +785,7 @@
         <v>2.5</v>
       </c>
       <c r="N5" t="n">
-        <v>9.81</v>
+        <v>15.24</v>
       </c>
       <c r="O5" t="n">
         <v>0.95</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,19 +833,19 @@
         <v>17.69</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44739.55208333334</v>
+        <v>44740.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>65.84999999999999</v>
+        <v>60.75</v>
       </c>
       <c r="I6" t="n">
         <v>63.40235224508176</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K6" t="n">
-        <v>2.97</v>
+        <v>-5</v>
       </c>
       <c r="L6" t="n">
         <v>9.380000000000001</v>
@@ -783,7 +854,7 @@
         <v>4.75</v>
       </c>
       <c r="N6" t="n">
-        <v>6.46</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="O6" t="n">
         <v>15.24</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,28 +902,28 @@
         <v>18.99</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44774.55208333334</v>
+        <v>44775.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>46.5</v>
+        <v>54.4</v>
       </c>
       <c r="I7" t="n">
         <v>48.73627073927489</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K7" t="n">
-        <v>23.46</v>
+        <v>10.45</v>
       </c>
       <c r="L7" t="n">
         <v>8.15</v>
       </c>
       <c r="M7" t="n">
-        <v>2.16</v>
+        <v>7.53</v>
       </c>
       <c r="N7" t="n">
-        <v>5.65</v>
+        <v>19.46</v>
       </c>
       <c r="O7" t="n">
         <v>-8.050000000000001</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>3</v>
+      </c>
+      <c r="U7" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>19.82</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44802.55208333334</v>
+        <v>44803.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>59.25</v>
+        <v>57.6</v>
       </c>
       <c r="I8" t="n">
         <v>59.193418699484</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K8" t="n">
-        <v>8.92</v>
+        <v>5.88</v>
       </c>
       <c r="L8" t="n">
         <v>11.03</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44798</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -933,22 +1040,22 @@
         <v>15.38</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44816.55208333334</v>
+        <v>44817.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>62.65</v>
+        <v>65.55</v>
       </c>
       <c r="I9" t="n">
         <v>64.62165993464005</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K9" t="n">
-        <v>-8.77</v>
+        <v>-13.8</v>
       </c>
       <c r="L9" t="n">
-        <v>10.5</v>
+        <v>15.54</v>
       </c>
       <c r="M9" t="n">
         <v>1.6</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,28 +1109,28 @@
         <v>9.16</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44827.55208333334</v>
+        <v>44830.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>60.8</v>
+        <v>58.95</v>
       </c>
       <c r="I10" t="n">
         <v>60.73221584301058</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K10" t="n">
-        <v>-7.25</v>
+        <v>-10.07</v>
       </c>
       <c r="L10" t="n">
-        <v>7.78</v>
+        <v>12.28</v>
       </c>
       <c r="M10" t="n">
         <v>2.14</v>
       </c>
       <c r="N10" t="n">
-        <v>3.8</v>
+        <v>5.26</v>
       </c>
       <c r="O10" t="n">
         <v>4.47</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S10" t="b">
+        <v>0</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -1047,25 +1178,25 @@
         <v>9.130000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44837.55208333334</v>
+        <v>44838.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>61.75</v>
+        <v>63.95</v>
       </c>
       <c r="I11" t="n">
         <v>63.19833958262881</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K11" t="n">
-        <v>-4.75</v>
+        <v>-8.48</v>
       </c>
       <c r="L11" t="n">
-        <v>7.04</v>
+        <v>9.33</v>
       </c>
       <c r="M11" t="n">
-        <v>1.72</v>
+        <v>2.19</v>
       </c>
       <c r="N11" t="n">
         <v>6.19</v>
@@ -1077,7 +1208,19 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,22 +1247,22 @@
         <v>9.34</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44846.55208333334</v>
+        <v>44847.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>63.55</v>
+        <v>61.8</v>
       </c>
       <c r="I12" t="n">
         <v>63.03281247464231</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.63</v>
+        <v>-3.36</v>
       </c>
       <c r="L12" t="n">
-        <v>1.49</v>
+        <v>3.67</v>
       </c>
       <c r="M12" t="n">
         <v>1.23</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>12.47</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44872.55208333334</v>
+        <v>44874.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>64.90000000000001</v>
+        <v>66.05</v>
       </c>
       <c r="I13" t="n">
         <v>65.87521756491461</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K13" t="n">
-        <v>-5.02</v>
+        <v>-6.88</v>
       </c>
       <c r="L13" t="n">
-        <v>6.31</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="M13" t="n">
         <v>2.11</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>5.71</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44886.55208333334</v>
+        <v>44887.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>64.34999999999999</v>
+        <v>64.15000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>64.26086299527446</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>12.16666666666667</v>
+        <v>13</v>
       </c>
       <c r="K14" t="n">
-        <v>-2.57</v>
+        <v>-2.88</v>
       </c>
       <c r="L14" t="n">
         <v>4.39</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>9.19</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44896.55208333334</v>
+        <v>44897.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>66.5</v>
+        <v>68.05</v>
       </c>
       <c r="I15" t="n">
         <v>67.49715895979749</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.66</v>
+        <v>-6.08</v>
       </c>
       <c r="L15" t="n">
-        <v>4.68</v>
+        <v>6.63</v>
       </c>
       <c r="M15" t="n">
         <v>1.14</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,22 +1523,22 @@
         <v>8.27</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44910.55208333334</v>
+        <v>44911.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>63.9</v>
+        <v>63.05</v>
       </c>
       <c r="I16" t="n">
         <v>63.57313307866202</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.1</v>
+        <v>-7.35</v>
       </c>
       <c r="L16" t="n">
-        <v>6.54</v>
+        <v>7.71</v>
       </c>
       <c r="M16" t="n">
         <v>0.84</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,19 +1592,19 @@
         <v>5.13</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44923.38541666666</v>
+        <v>44923.55208333334</v>
       </c>
       <c r="H17" t="n">
-        <v>59.3</v>
+        <v>60</v>
       </c>
       <c r="I17" t="n">
         <v>59.49292916003334</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K17" t="n">
-        <v>5.95</v>
+        <v>4.84</v>
       </c>
       <c r="L17" t="n">
         <v>1.51</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,22 +1661,22 @@
         <v>9.48</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44931.55208333334</v>
+        <v>44932.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>56.35</v>
+        <v>55.4</v>
       </c>
       <c r="I18" t="n">
         <v>55.61683405989829</v>
       </c>
       <c r="J18" s="2" t="n">
+        <v>8.833333333333334</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-7.67</v>
+      </c>
+      <c r="L18" t="n">
         <v>8</v>
-      </c>
-      <c r="K18" t="n">
-        <v>-6.08</v>
-      </c>
-      <c r="L18" t="n">
-        <v>7.33</v>
       </c>
       <c r="M18" t="n">
         <v>2.32</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>2</v>
+      </c>
+      <c r="U18" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>8.24</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>44964.55208333334</v>
+        <v>44965.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>50.5</v>
+        <v>53.1</v>
       </c>
       <c r="I19" t="n">
         <v>52.87635141772957</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K19" t="n">
-        <v>8.84</v>
+        <v>4.15</v>
       </c>
       <c r="L19" t="n">
         <v>3.25</v>
@@ -1524,7 +1751,7 @@
         <v>5.49</v>
       </c>
       <c r="N19" t="n">
-        <v>5.76</v>
+        <v>6.44</v>
       </c>
       <c r="O19" t="n">
         <v>-1.6</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>42</v>
+        <v>43</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>2</v>
+      </c>
+      <c r="U19" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>11.97</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>44998.55208333334</v>
+        <v>44999.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>51.75</v>
+        <v>50.75</v>
       </c>
       <c r="I20" t="n">
         <v>51.51908876764567</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K20" t="n">
-        <v>-2.54</v>
+        <v>-4.43</v>
       </c>
       <c r="L20" t="n">
         <v>6.21</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>9.539999999999999</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45002.38541666666</v>
+        <v>45002.55208333334</v>
       </c>
       <c r="H21" t="n">
-        <v>53.6</v>
+        <v>55.3</v>
       </c>
       <c r="I21" t="n">
         <v>54.70450174535431</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.62</v>
+        <v>-8.970000000000001</v>
       </c>
       <c r="L21" t="n">
-        <v>7.29</v>
+        <v>9.66</v>
       </c>
       <c r="M21" t="n">
         <v>1.28</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,22 +1937,22 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45012.55208333334</v>
+        <v>45013.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>50.05</v>
+        <v>49.55</v>
       </c>
       <c r="I22" t="n">
         <v>49.98788140487304</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K22" t="n">
-        <v>-9.49</v>
+        <v>-10.4</v>
       </c>
       <c r="L22" t="n">
-        <v>10.94</v>
+        <v>11.39</v>
       </c>
       <c r="M22" t="n">
         <v>3.07</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S22" t="b">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>1</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -1731,28 +2006,28 @@
         <v>8.880000000000001</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45022.55208333334</v>
+        <v>45026.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>52.1</v>
+        <v>53.95</v>
       </c>
       <c r="I23" t="n">
         <v>53.94962161010571</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>13</v>
       </c>
       <c r="K23" t="n">
-        <v>-5.15</v>
+        <v>-8.880000000000001</v>
       </c>
       <c r="L23" t="n">
-        <v>6.66</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="M23" t="n">
         <v>0.78</v>
       </c>
       <c r="N23" t="n">
-        <v>1.57</v>
+        <v>3.36</v>
       </c>
       <c r="O23" t="n">
         <v>0.7</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>8.16</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45113.55208333334</v>
+        <v>45114.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>74.7</v>
+        <v>73.2</v>
       </c>
       <c r="I24" t="n">
         <v>73.87690242048852</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>87.16666666666667</v>
+        <v>88</v>
       </c>
       <c r="K24" t="n">
-        <v>38.46</v>
+        <v>35.68</v>
       </c>
       <c r="L24" t="n">
         <v>3.99</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>122</v>
+        <v>123</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>4</v>
+      </c>
+      <c r="U24" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>6.63</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45118.55208333334</v>
+        <v>45119.38541666666</v>
       </c>
       <c r="H25" t="n">
-        <v>76.84999999999999</v>
+        <v>77.84999999999999</v>
       </c>
       <c r="I25" t="n">
         <v>77.08633338675949</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K25" t="n">
-        <v>-4.99</v>
+        <v>-6.35</v>
       </c>
       <c r="L25" t="n">
-        <v>5.19</v>
+        <v>7.65</v>
       </c>
       <c r="M25" t="n">
         <v>1.01</v>
@@ -1875,7 +2174,19 @@
         <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>5.14</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45222.55208333334</v>
+        <v>45224.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>109.25</v>
+        <v>106.3</v>
       </c>
       <c r="I26" t="n">
         <v>107.3429039075307</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>103.1666666666667</v>
+        <v>105</v>
       </c>
       <c r="K26" t="n">
-        <v>40.33</v>
+        <v>36.54</v>
       </c>
       <c r="L26" t="n">
         <v>1.73</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>142</v>
+        <v>143</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>4</v>
+      </c>
+      <c r="U26" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="27">
@@ -1959,22 +2282,22 @@
         <v>9.279999999999999</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45233.38541666666</v>
+        <v>45233.55208333334</v>
       </c>
       <c r="H27" t="n">
-        <v>111.95</v>
+        <v>117.9</v>
       </c>
       <c r="I27" t="n">
         <v>112.6974064994665</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K27" t="n">
-        <v>-5.32</v>
+        <v>-10.91</v>
       </c>
       <c r="L27" t="n">
-        <v>6.07</v>
+        <v>12.79</v>
       </c>
       <c r="M27" t="n">
         <v>0.99</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>10.71</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45252.38541666666</v>
+        <v>45252.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>115.95</v>
+        <v>115.5</v>
       </c>
       <c r="I28" t="n">
         <v>115.8407109822106</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>18.83333333333333</v>
+        <v>19</v>
       </c>
       <c r="K28" t="n">
-        <v>-1.65</v>
+        <v>-2.04</v>
       </c>
       <c r="L28" t="n">
         <v>5.13</v>
@@ -2046,7 +2381,19 @@
         <v>1</v>
       </c>
       <c r="Q28" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,22 +2420,22 @@
         <v>6.35</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45266.55208333334</v>
+        <v>45267.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>119.15</v>
+        <v>121.55</v>
       </c>
       <c r="I29" t="n">
         <v>120.6640266317456</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>14</v>
+        <v>14.83333333333333</v>
       </c>
       <c r="K29" t="n">
-        <v>-3.16</v>
+        <v>-5.24</v>
       </c>
       <c r="L29" t="n">
-        <v>4.5</v>
+        <v>5.41</v>
       </c>
       <c r="M29" t="n">
         <v>2.81</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>7.14</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45306.55208333334</v>
+        <v>45307.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>133.75</v>
+        <v>131.5</v>
       </c>
       <c r="I30" t="n">
         <v>131.5199756652898</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>39.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K30" t="n">
-        <v>10.04</v>
+        <v>8.19</v>
       </c>
       <c r="L30" t="n">
         <v>6.09</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>2</v>
+      </c>
+      <c r="U30" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>9.06</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45320.55208333334</v>
+        <v>45321.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>135</v>
+        <v>137.8</v>
       </c>
       <c r="I31" t="n">
         <v>136.2418597718448</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K31" t="n">
-        <v>-2.66</v>
+        <v>-4.79</v>
       </c>
       <c r="L31" t="n">
-        <v>5.1</v>
+        <v>5.55</v>
       </c>
       <c r="M31" t="n">
         <v>1.64</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>9.58</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45358.55208333334</v>
+        <v>45362.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>160.3</v>
+        <v>154.5</v>
       </c>
       <c r="I32" t="n">
         <v>154.6214255699694</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>41</v>
       </c>
       <c r="K32" t="n">
-        <v>16.33</v>
+        <v>12.12</v>
       </c>
       <c r="L32" t="n">
         <v>2.29</v>
@@ -2265,7 +2648,7 @@
         <v>1.41</v>
       </c>
       <c r="N32" t="n">
-        <v>3.03</v>
+        <v>3.37</v>
       </c>
       <c r="O32" t="n">
         <v>1.52</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>12.44</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45371.55208333334</v>
+        <v>45372.38541666666</v>
       </c>
       <c r="H33" t="n">
-        <v>166</v>
+        <v>169.65</v>
       </c>
       <c r="I33" t="n">
         <v>167.297403045189</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K33" t="n">
-        <v>-7.44</v>
+        <v>-9.81</v>
       </c>
       <c r="L33" t="n">
-        <v>7.9</v>
+        <v>10.68</v>
       </c>
       <c r="M33" t="n">
         <v>1.75</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>9.83</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>196.15</v>
+        <v>183.15</v>
       </c>
       <c r="I34" t="n">
         <v>186.0509840730184</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>46.16666666666666</v>
+        <v>47</v>
       </c>
       <c r="K34" t="n">
-        <v>15.62</v>
+        <v>7.96</v>
       </c>
       <c r="L34" t="n">
         <v>1.92</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S34" t="b">
+        <v>1</v>
+      </c>
+      <c r="T34" t="n">
+        <v>3</v>
+      </c>
+      <c r="U34" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>11.59</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45449.55208333334</v>
+        <v>45450.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>183.35</v>
+        <v>186.05</v>
       </c>
       <c r="I35" t="n">
         <v>185.135938277546</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.11</v>
+        <v>-1.58</v>
       </c>
       <c r="L35" t="n">
         <v>13.13</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>12.91</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45534.55208333334</v>
+        <v>45537.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>251.45</v>
+        <v>244.05</v>
       </c>
       <c r="I36" t="n">
         <v>249.2473065771276</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>84.16666666666667</v>
+        <v>87</v>
       </c>
       <c r="K36" t="n">
-        <v>35.15</v>
+        <v>31.17</v>
       </c>
       <c r="L36" t="n">
         <v>3.61</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>116</v>
+        <v>117</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>4</v>
+      </c>
+      <c r="U36" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>8.6</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45540.55208333334</v>
+        <v>45541.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>254.9</v>
+        <v>259.9</v>
       </c>
       <c r="I37" t="n">
         <v>259.1131446474531</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.45</v>
+        <v>-6.49</v>
       </c>
       <c r="L37" t="n">
-        <v>7.19</v>
+        <v>7.42</v>
       </c>
       <c r="M37" t="n">
         <v>1.78</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S37" t="b">
+        <v>0</v>
+      </c>
+      <c r="T37" t="n">
+        <v>1</v>
+      </c>
+      <c r="U37" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>8.19</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45562.55208333334</v>
+        <v>45565.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>278</v>
+        <v>273.5</v>
       </c>
       <c r="I38" t="n">
         <v>273.9477992684522</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K38" t="n">
-        <v>6.96</v>
+        <v>5.23</v>
       </c>
       <c r="L38" t="n">
         <v>2.17</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>8.44</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45609.55208333334</v>
+        <v>45610.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>259.2</v>
+        <v>268.24</v>
       </c>
       <c r="I39" t="n">
         <v>263.2579017668923</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>44.16666666666666</v>
+        <v>45</v>
       </c>
       <c r="K39" t="n">
-        <v>5.23</v>
+        <v>1.92</v>
       </c>
       <c r="L39" t="n">
         <v>6.03</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>2</v>
+      </c>
+      <c r="U39" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="40">
@@ -2700,19 +3179,19 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45646.38541666666</v>
+        <v>45646.55208333334</v>
       </c>
       <c r="H40" t="n">
-        <v>285</v>
+        <v>274.8</v>
       </c>
       <c r="I40" t="n">
         <v>281.3395826050019</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K40" t="n">
-        <v>6.25</v>
+        <v>2.45</v>
       </c>
       <c r="L40" t="n">
         <v>2.81</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>9.23</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45674.55208333334</v>
+        <v>45677.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>248.65</v>
+        <v>253.15</v>
       </c>
       <c r="I41" t="n">
         <v>249.728146272561</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>28</v>
+        <v>30.83333333333333</v>
       </c>
       <c r="K41" t="n">
-        <v>9.52</v>
+        <v>7.88</v>
       </c>
       <c r="L41" t="n">
         <v>6.11</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,25 +3317,25 @@
         <v>10.12</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45677.55208333334</v>
+        <v>45678.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>230.45</v>
+        <v>218.65</v>
       </c>
       <c r="I42" t="n">
         <v>227.5246515091959</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>0.1666666666666667</v>
+        <v>1</v>
       </c>
       <c r="K42" t="n">
-        <v>-8.970000000000001</v>
+        <v>-13.63</v>
       </c>
       <c r="L42" t="n">
-        <v>9.84</v>
+        <v>17.91</v>
       </c>
       <c r="M42" t="n">
-        <v>-0</v>
+        <v>3.23</v>
       </c>
       <c r="N42" t="n">
         <v>7.32</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,22 +3386,22 @@
         <v>14.08</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45688.55208333334</v>
+        <v>45689.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>222.1</v>
+        <v>232.97</v>
       </c>
       <c r="I43" t="n">
         <v>231.4306259648162</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K43" t="n">
-        <v>-1.58</v>
+        <v>-6.55</v>
       </c>
       <c r="L43" t="n">
-        <v>3.82</v>
+        <v>6.68</v>
       </c>
       <c r="M43" t="n">
         <v>0.86</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>13.44</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45723.55208333334</v>
+        <v>45726.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>217.09</v>
+        <v>214.2</v>
       </c>
       <c r="I44" t="n">
         <v>216.2867973556366</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>37</v>
       </c>
       <c r="K44" t="n">
-        <v>-6.82</v>
+        <v>-8.06</v>
       </c>
       <c r="L44" t="n">
         <v>11.25</v>
@@ -2958,7 +3485,19 @@
         <v>1</v>
       </c>
       <c r="Q44" t="n">
-        <v>50</v>
+        <v>51</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>2</v>
+      </c>
+      <c r="U44" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45734.55208333334</v>
+        <v>45735.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>218.91</v>
+        <v>226.05</v>
       </c>
       <c r="I45" t="n">
         <v>219.8344155042314</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K45" t="n">
-        <v>-2.2</v>
+        <v>-5.53</v>
       </c>
       <c r="L45" t="n">
-        <v>2.29</v>
+        <v>6.21</v>
       </c>
       <c r="M45" t="n">
         <v>1.19</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>10.01</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45741.55208333334</v>
+        <v>45742.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>209.53</v>
+        <v>204.57</v>
       </c>
       <c r="I46" t="n">
         <v>209.5235352053334</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K46" t="n">
-        <v>-7.31</v>
+        <v>-9.5</v>
       </c>
       <c r="L46" t="n">
-        <v>7.54</v>
+        <v>11.56</v>
       </c>
       <c r="M46" t="n">
-        <v>1.79</v>
+        <v>3.43</v>
       </c>
       <c r="N46" t="n">
         <v>5.97</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S46" t="b">
+        <v>0</v>
+      </c>
+      <c r="T46" t="n">
+        <v>1</v>
+      </c>
+      <c r="U46" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -3099,25 +3662,25 @@
         <v>8.82</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45758.55208333334</v>
+        <v>45762.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>216</v>
+        <v>222.67</v>
       </c>
       <c r="I47" t="n">
         <v>218.9263647982385</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K47" t="n">
-        <v>-5.59</v>
+        <v>-8.85</v>
       </c>
       <c r="L47" t="n">
-        <v>7.15</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="M47" t="n">
-        <v>2.37</v>
+        <v>3.82</v>
       </c>
       <c r="N47" t="n">
         <v>3.77</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>2</v>
+      </c>
+      <c r="U47" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>8.6</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45797.38541666666</v>
+        <v>45797.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>229.22</v>
+        <v>228</v>
       </c>
       <c r="I48" t="n">
         <v>229.0233413781317</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>35</v>
+        <v>35.16666666666666</v>
       </c>
       <c r="K48" t="n">
-        <v>2.94</v>
+        <v>2.39</v>
       </c>
       <c r="L48" t="n">
         <v>1.92</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>8.029999999999999</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45807.38541666666</v>
+        <v>45807.55208333334</v>
       </c>
       <c r="H49" t="n">
-        <v>236.68</v>
+        <v>239.99</v>
       </c>
       <c r="I49" t="n">
         <v>238.7634078954087</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>9.833333333333334</v>
+        <v>10</v>
       </c>
       <c r="K49" t="n">
-        <v>-3.81</v>
+        <v>-5.26</v>
       </c>
       <c r="L49" t="n">
-        <v>5.57</v>
+        <v>6.58</v>
       </c>
       <c r="M49" t="n">
         <v>0.61</v>
@@ -3243,7 +3830,19 @@
         <v>1</v>
       </c>
       <c r="Q49" t="n">
-        <v>16</v>
+        <v>17</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>2</v>
+      </c>
+      <c r="U49" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>7.55</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45855.55208333334</v>
+        <v>45856.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>259.75</v>
+        <v>257.2</v>
       </c>
       <c r="I50" t="n">
         <v>257.7058430055549</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K50" t="n">
-        <v>8.23</v>
+        <v>7.17</v>
       </c>
       <c r="L50" t="n">
         <v>2.48</v>
@@ -3300,7 +3899,19 @@
         <v>1</v>
       </c>
       <c r="Q50" t="n">
-        <v>69</v>
+        <v>70</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>5.35</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45859.38541666666</v>
+        <v>45859.55208333334</v>
       </c>
       <c r="H51" t="n">
-        <v>264.15</v>
+        <v>276.5</v>
       </c>
       <c r="I51" t="n">
         <v>268.9462677852007</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K51" t="n">
-        <v>-2.7</v>
+        <v>-7.5</v>
       </c>
       <c r="L51" t="n">
-        <v>3.29</v>
+        <v>7.7</v>
       </c>
       <c r="M51" t="n">
         <v>0.08</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S51" t="b">
+        <v>0</v>
+      </c>
+      <c r="T51" t="n">
+        <v>1</v>
+      </c>
+      <c r="U51" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>8.619999999999999</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45925.55208333334</v>
+        <v>45926.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>332.55</v>
+        <v>325.35</v>
       </c>
       <c r="I52" t="n">
         <v>328.7952053991313</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>66</v>
+        <v>66.83333333333333</v>
       </c>
       <c r="K52" t="n">
-        <v>20.27</v>
+        <v>17.67</v>
       </c>
       <c r="L52" t="n">
         <v>5.5</v>
@@ -3405,7 +4028,7 @@
         <v>2.83</v>
       </c>
       <c r="N52" t="n">
-        <v>1.96</v>
+        <v>2.93</v>
       </c>
       <c r="O52" t="n">
         <v>7.3</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>93</v>
+        <v>94</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
@@ -3441,22 +4076,22 @@
         <v>5.24</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45936.55208333334</v>
+        <v>45937.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>335.6</v>
+        <v>338.75</v>
       </c>
       <c r="I53" t="n">
         <v>336.393676060459</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K53" t="n">
-        <v>-3.15</v>
+        <v>-4.12</v>
       </c>
       <c r="L53" t="n">
-        <v>3.37</v>
+        <v>4.99</v>
       </c>
       <c r="M53" t="n">
         <v>1.29</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>5.25</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45946.38541666666</v>
+        <v>45946.55208333334</v>
       </c>
       <c r="H54" t="n">
-        <v>356.7</v>
+        <v>340.3</v>
       </c>
       <c r="I54" t="n">
         <v>341.5161894715502</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>9</v>
+        <v>9.166666666666666</v>
       </c>
       <c r="K54" t="n">
-        <v>5.3</v>
+        <v>0.46</v>
       </c>
       <c r="L54" t="n">
         <v>1.64</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>10.6</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46034.55208333334</v>
+        <v>46035.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>285.2</v>
+        <v>290.95</v>
       </c>
       <c r="I55" t="n">
         <v>288.3282594679042</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>88</v>
+        <v>88.83333333333333</v>
       </c>
       <c r="K55" t="n">
-        <v>16.19</v>
+        <v>14.5</v>
       </c>
       <c r="L55" t="n">
         <v>8.27</v>
       </c>
       <c r="M55" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="N55" t="n">
-        <v>2.71</v>
+        <v>3.17</v>
       </c>
       <c r="O55" t="n">
         <v>-4.25</v>
@@ -3585,7 +4244,19 @@
         <v>1</v>
       </c>
       <c r="Q55" t="n">
-        <v>118</v>
+        <v>119</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>4</v>
+      </c>
+      <c r="U55" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
@@ -3612,22 +4283,22 @@
         <v>5.32</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46038.55208333334</v>
+        <v>46041.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="I56" t="n">
         <v>280.0846119503616</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K56" t="n">
-        <v>-1.01</v>
+        <v>-4.45</v>
       </c>
       <c r="L56" t="n">
-        <v>1.43</v>
+        <v>4.55</v>
       </c>
       <c r="M56" t="n">
         <v>1.75</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S56" t="b">
+        <v>0</v>
+      </c>
+      <c r="T56" t="n">
+        <v>1</v>
+      </c>
+      <c r="U56" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -3669,25 +4352,25 @@
         <v>9.58</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>273.75</v>
+        <v>283.7</v>
       </c>
       <c r="I57" t="n">
         <v>280.1019747521165</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K57" t="n">
-        <v>1.53</v>
+        <v>-2.05</v>
       </c>
       <c r="L57" t="n">
         <v>9.710000000000001</v>
       </c>
       <c r="M57" t="n">
-        <v>6.08</v>
+        <v>7.4</v>
       </c>
       <c r="N57" t="n">
         <v>4.57</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.220000000000001</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46069.55208333334</v>
+        <v>46070.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>286.35</v>
+        <v>279.15</v>
       </c>
       <c r="I58" t="n">
         <v>279.7151398365813</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K58" t="n">
-        <v>0.93</v>
+        <v>-1.6</v>
       </c>
       <c r="L58" t="n">
         <v>3.75</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>0</v>
+      </c>
+      <c r="T58" t="n">
+        <v>1</v>
+      </c>
+      <c r="U58" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -3783,19 +4490,19 @@
         <v>8.27</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46097.55208333334</v>
+        <v>46098.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>222.5</v>
+        <v>234.35</v>
       </c>
       <c r="I59" t="n">
         <v>233.1352453146615</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K59" t="n">
-        <v>20.29</v>
+        <v>16.05</v>
       </c>
       <c r="L59" t="n">
         <v>1.97</v>
@@ -3804,7 +4511,7 @@
         <v>1.66</v>
       </c>
       <c r="N59" t="n">
-        <v>2.53</v>
+        <v>5.26</v>
       </c>
       <c r="O59" t="n">
         <v>-1.59</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>11.13</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46141.55208333334</v>
+        <v>46142.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>253.43</v>
+        <v>244.69</v>
       </c>
       <c r="I60" t="n">
         <v>247.3183683988009</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>43.16666666666666</v>
+        <v>44</v>
       </c>
       <c r="K60" t="n">
-        <v>8.140000000000001</v>
+        <v>4.41</v>
       </c>
       <c r="L60" t="n">
         <v>4.95</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>56</v>
+        <v>57</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,19 +4628,19 @@
         <v>10.11</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46168.55208333334</v>
+        <v>46169.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>251</v>
+        <v>253.74</v>
       </c>
       <c r="I61" t="n">
         <v>251.7507450134174</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K61" t="n">
-        <v>-2.58</v>
+        <v>-3.7</v>
       </c>
       <c r="L61" t="n">
         <v>6.47</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>5.47</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46183.38541666666</v>
+        <v>46183.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>244.6</v>
+        <v>239.85</v>
       </c>
       <c r="I62" t="n">
         <v>242.1765716602879</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>14</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-3.6</v>
+        <v>-5.47</v>
       </c>
       <c r="L62" t="n">
-        <v>4.35</v>
+        <v>5.81</v>
       </c>
       <c r="M62" t="n">
         <v>1.71</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,25 +4766,25 @@
         <v>7.26</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>244.05</v>
+        <v>254.6</v>
       </c>
       <c r="I63" t="n">
         <v>251.6221387006673</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>2</v>
+        <v>4.833333333333333</v>
       </c>
       <c r="K63" t="n">
-        <v>-1.75</v>
+        <v>-6.15</v>
       </c>
       <c r="L63" t="n">
-        <v>1.98</v>
+        <v>7</v>
       </c>
       <c r="M63" t="n">
-        <v>1.38</v>
+        <v>2.44</v>
       </c>
       <c r="N63" t="n">
         <v>3.52</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>0</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1</v>
+      </c>
+      <c r="U63" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>8.050000000000001</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46280.38541666666</v>
+        <v>46280.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>318.05</v>
+        <v>316.6</v>
       </c>
       <c r="I64" t="n">
         <v>316.9071730566922</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>92</v>
+        <v>92.16666666666667</v>
       </c>
       <c r="K64" t="n">
-        <v>24.92</v>
+        <v>24.35</v>
       </c>
       <c r="L64" t="n">
         <v>2.57</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>4</v>
+      </c>
+      <c r="U64" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="65">
@@ -4125,28 +4904,28 @@
         <v>4.58</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46283.55208333334</v>
+        <v>46286.38541666666</v>
       </c>
       <c r="H65" t="n">
-        <v>328</v>
+        <v>331.5</v>
       </c>
       <c r="I65" t="n">
         <v>329.9976364057088</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.6</v>
+        <v>-4.71</v>
       </c>
       <c r="L65" t="n">
-        <v>4.15</v>
+        <v>4.99</v>
       </c>
       <c r="M65" t="n">
         <v>1.67</v>
       </c>
       <c r="N65" t="n">
-        <v>1.8</v>
+        <v>2.26</v>
       </c>
       <c r="O65" t="n">
         <v>-1.91</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S65" t="b">
+        <v>0</v>
+      </c>
+      <c r="T65" t="n">
+        <v>1</v>
+      </c>
+      <c r="U65" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -4182,22 +4973,22 @@
         <v>5.06</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46293.55208333334</v>
+        <v>46294.38541666666</v>
       </c>
       <c r="H66" t="n">
-        <v>331.25</v>
+        <v>324</v>
       </c>
       <c r="I66" t="n">
         <v>329.0073450361172</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K66" t="n">
-        <v>-0.08</v>
+        <v>-2.26</v>
       </c>
       <c r="L66" t="n">
-        <v>1.4</v>
+        <v>2.37</v>
       </c>
       <c r="M66" t="n">
         <v>1.04</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,28 +5042,28 @@
         <v>6.22</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46300.55208333334</v>
+        <v>46301.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>320</v>
+        <v>329.15</v>
       </c>
       <c r="I67" t="n">
         <v>328.7702068472062</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K67" t="n">
-        <v>1.23</v>
+        <v>-1.59</v>
       </c>
       <c r="L67" t="n">
         <v>2.78</v>
       </c>
       <c r="M67" t="n">
-        <v>0.53</v>
+        <v>0.78</v>
       </c>
       <c r="N67" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="O67" t="n">
         <v>-0.83</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S67" t="b">
+        <v>0</v>
+      </c>
+      <c r="T67" t="n">
+        <v>1</v>
+      </c>
+      <c r="U67" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>7.36</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46314.55208333334</v>
+        <v>46316.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>320.55</v>
+        <v>309.5</v>
       </c>
       <c r="I68" t="n">
         <v>310.3053859029138</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>15</v>
       </c>
       <c r="K68" t="n">
-        <v>-2.61</v>
+        <v>-5.97</v>
       </c>
       <c r="L68" t="n">
-        <v>4.72</v>
+        <v>6.06</v>
       </c>
       <c r="M68" t="n">
         <v>0.18</v>
       </c>
       <c r="N68" t="n">
-        <v>2.85</v>
+        <v>3.67</v>
       </c>
       <c r="O68" t="n">
         <v>2.75</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S68" t="b">
+        <v>0</v>
+      </c>
+      <c r="T68" t="n">
+        <v>1</v>
+      </c>
+      <c r="U68" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="69">
@@ -4377,6 +5204,12 @@
       <c r="Q69" t="n">
         <v>10</v>
       </c>
+      <c r="R69" s="3" t="n">
+        <v>46322</v>
+      </c>
+      <c r="S69" t="inlineStr"/>
+      <c r="T69" t="inlineStr"/>
+      <c r="U69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6479,7 +7312,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24.9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6">
@@ -6489,7 +7322,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>14.8</v>
       </c>
     </row>
     <row r="7">
@@ -6499,7 +7332,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>103.2</v>
+        <v>105</v>
       </c>
     </row>
     <row r="8">
@@ -6509,7 +7342,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
@@ -6519,7 +7352,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>34.2</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -6529,7 +7362,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>55.2</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
@@ -6539,7 +7372,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -6549,7 +7382,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="13">
@@ -6559,7 +7392,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>68.7</v>
+        <v>67.2</v>
       </c>
     </row>
     <row r="14">
@@ -6569,7 +7402,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.64</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="15">
@@ -6579,7 +7412,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.18</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="16">
@@ -6589,7 +7422,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.05</v>
+        <v>-1.33</v>
       </c>
     </row>
     <row r="17">
@@ -6599,7 +7432,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>40.33</v>
+        <v>36.54</v>
       </c>
     </row>
     <row r="18">
@@ -6609,7 +7442,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41.8</v>
+        <v>35.8</v>
       </c>
     </row>
     <row r="19">
@@ -6619,7 +7452,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>5.25</v>
+        <v>6.48</v>
       </c>
     </row>
     <row r="20">
@@ -6629,7 +7462,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.95</v>
+        <v>6.09</v>
       </c>
     </row>
     <row r="21">
@@ -6639,7 +7472,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.13</v>
+        <v>17.91</v>
       </c>
     </row>
     <row r="22">
@@ -6649,7 +7482,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>33</v>
+        <v>41</v>
       </c>
     </row>
     <row r="23">
@@ -6659,7 +7492,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="24">
@@ -6669,7 +7502,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="25">
@@ -6679,7 +7512,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>6.08</v>
+        <v>7.53</v>
       </c>
     </row>
     <row r="26">
@@ -6689,7 +7522,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>4.68</v>
+        <v>5.14</v>
       </c>
     </row>
     <row r="27">
@@ -6699,7 +7532,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.45</v>
+        <v>19.46</v>
       </c>
     </row>
     <row r="28">
@@ -6709,7 +7542,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
